--- a/tests/fixtures/baseline/paydetail-06__shenbianyun-cur/002.xlsx
+++ b/tests/fixtures/baseline/paydetail-06__shenbianyun-cur/002.xlsx
@@ -4,17 +4,19 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="个人银行账户批量付款模板" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="52">
   <si>
     <t xml:space="preserve">单批次最大支持12000条订单。
 商户订单号纯数字并且唯一，禁止重复。
+多任务模式时任务ID必填（单次最多50个任务），单任务模式时不可填任务ID。
+收款账号需要与所选收款方式对应匹配，银行卡方式对应个人银行卡号、支付宝方式对应支付宝号、微信方式对应OpenID。
 付款金额保留两位小数，四舍五入。
 备注字段最大限制20字，银行备注展示限制具体以银行为准。
 付款文件名称或备注存在以下字段会导致文件上传失败：工资、薪酬、提现、薪、补贴、分红、奖金、返现、劳务费、分润、备用金、¥、$
@@ -24,25 +26,22 @@
     <t>商户批次号（非必填）</t>
   </si>
   <si>
-    <t>总笔数（非必填）</t>
-  </si>
-  <si>
-    <t>总金额（元，非必填）</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
     <t>商户订单号（非必填）</t>
   </si>
   <si>
+    <t>任务ID（条件必填）</t>
+  </si>
+  <si>
     <t>收款人姓名（必填）</t>
   </si>
   <si>
     <t>身份证号（必填）</t>
   </si>
   <si>
-    <t>个人银行卡号（必填）</t>
+    <t>收款账号（条件必填）</t>
   </si>
   <si>
     <t>付款金额（元，必填）</t>
@@ -203,11 +202,11 @@
       <name val="微软雅黑"/>
     </font>
     <font>
+      <color rgb="FF006100"/>
       <sz val="12"/>
       <name val="微软雅黑"/>
     </font>
     <font>
-      <color rgb="FF006100"/>
       <sz val="12"/>
       <name val="微软雅黑"/>
     </font>
@@ -250,16 +249,16 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -601,18 +600,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="20.15" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="26.08" customWidth="1"/>
-    <col min="4" max="6" width="20.15" customWidth="1"/>
-    <col min="7" max="7" width="14.39" customWidth="1"/>
-    <col min="8" max="8" width="22.45" customWidth="1"/>
+    <col min="1" max="1" width="22.6333333333333" customWidth="1"/>
+    <col min="2" max="2" width="20.6333333333333" customWidth="1"/>
+    <col min="3" max="3" width="22.6333333333333" customWidth="1"/>
+    <col min="4" max="4" width="20.5" customWidth="1"/>
+    <col min="5" max="5" width="27.5" customWidth="1"/>
+    <col min="6" max="6" width="22.6333333333333" customWidth="1"/>
+    <col min="7" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="22.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="121" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -623,422 +624,456 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="I4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="5" t="s">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="6">
+        <v>81300</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="3">
-        <v>81300</v>
-      </c>
-      <c r="F5" s="6" t="s">
+      <c r="H5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="6" t="s">
+      <c r="D6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="F6" s="6">
+        <v>63800</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="3">
-        <v>63800</v>
-      </c>
-      <c r="F6" s="6" t="s">
+      <c r="H6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="6" t="s">
+      <c r="D7" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="F7" s="6">
+        <v>19300</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="3">
-        <v>19300</v>
-      </c>
-      <c r="F7" s="6" t="s">
+      <c r="H7" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="6" t="s">
+      <c r="D8" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="F8" s="6">
+        <v>42000</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="3">
-        <v>42000</v>
-      </c>
-      <c r="F8" s="6" t="s">
+      <c r="H8" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="6" t="s">
+      <c r="D9" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="F9" s="6">
+        <v>34200</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="3">
-        <v>34200</v>
-      </c>
-      <c r="F9" s="6" t="s">
+      <c r="H9" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="s">
+      <c r="D10" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="F10" s="6">
+        <v>12600</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="3">
-        <v>12600</v>
-      </c>
-      <c r="F10" s="6" t="s">
+      <c r="H10" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="6" t="s">
+      <c r="D11" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="3" t="s">
+      <c r="F11" s="6">
+        <v>83800</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="3">
-        <v>83800</v>
-      </c>
-      <c r="F11" s="6" t="s">
+      <c r="H11" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="6" t="s">
+      <c r="D12" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="3" t="s">
+      <c r="F12" s="6">
+        <v>15400</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="3">
-        <v>15400</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="6" t="s">
+      <c r="D13" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="3" t="s">
+      <c r="F13" s="6">
+        <v>16900</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="3">
-        <v>16900</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="6" t="s">
+      <c r="D14" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="F14" s="6">
+        <v>9500</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="3">
-        <v>9500</v>
-      </c>
-      <c r="F14" s="6" t="s">
+      <c r="H14" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="6" t="s">
+      <c r="D15" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
+      <c r="F15" s="6">
+        <v>14300</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="3">
-        <v>14300</v>
-      </c>
-      <c r="F15" s="6" t="s">
+      <c r="H15" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="6" t="s">
+      <c r="D16" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="3" t="s">
+      <c r="F16" s="6">
+        <v>70800</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="3">
-        <v>70800</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="6" t="s">
+      <c r="D17" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="3" t="s">
+      <c r="F17" s="6">
+        <v>10400</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="3">
-        <v>10400</v>
-      </c>
-      <c r="F17" s="6" t="s">
+      <c r="H17" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="6" t="s">
+      <c r="D18" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="3" t="s">
+      <c r="F18" s="6">
+        <v>27200</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="3">
-        <v>27200</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>4</v>
+      <c r="H18" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
